--- a/StructureDefinition-ophthalmic-oct-macula.xlsx
+++ b/StructureDefinition-ophthalmic-oct-macula.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:13:42+00:00</t>
+    <t>2026-08-19T17:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-oct-macula.xlsx
+++ b/StructureDefinition-ophthalmic-oct-macula.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T00:41:24+00:00</t>
+    <t>2026-08-25T02:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-oct-macula.xlsx
+++ b/StructureDefinition-ophthalmic-oct-macula.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T02:25:39+00:00</t>
+    <t>2026-08-25T18:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-oct-macula.xlsx
+++ b/StructureDefinition-ophthalmic-oct-macula.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$258</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$262</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10015" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10168" uniqueCount="749">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:52:20+00:00</t>
+    <t>2026-09-01T17:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -289,7 +289,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}inv-oct-signal:OCT signal strength should be documented {component.where(code.text = 'Signal strength').exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -759,7 +759,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ophthalmic-encounter)
 </t>
   </si>
   <si>
@@ -1261,7 +1261,7 @@
 </t>
   </si>
   <si>
-    <t>(Measurement) Device</t>
+    <t>Acquisition device (manufacturer, model, software version)</t>
   </si>
   <si>
     <t>The device used to generate the observation data.</t>
@@ -2099,7 +2099,7 @@
     <t>Observation.component:thicknessDef.code</t>
   </si>
   <si>
-    <t>DICOM CID 4262, critical for device comparison</t>
+    <t>Retinal thickness definition - how thickness is defined (ILM to RPE or ILM to BM). DICOM CID 4262, critical for device comparison</t>
   </si>
   <si>
     <t>Observation.component:thicknessDef.value[x]</t>
@@ -2132,7 +2132,7 @@
     <t>Observation.component:deviationCategory.code</t>
   </si>
   <si>
-    <t>DICOM CID 4265</t>
+    <t>Thickness deviation category - normative database classification per subfield. DICOM CID 4265</t>
   </si>
   <si>
     <t>Observation.component:deviationCategory.value[x]</t>
@@ -2165,7 +2165,7 @@
     <t>Observation.component:anatomicRef.code</t>
   </si>
   <si>
-    <t>DICOM CID 4266</t>
+    <t>Anatomic reference point - structure used as reference (fovea or disc center). DICOM CID 4266</t>
   </si>
   <si>
     <t>Observation.component:anatomicRef.value[x]</t>
@@ -2198,7 +2198,7 @@
     <t>Observation.component:pupilDilated.code</t>
   </si>
   <si>
-    <t>DICOM (0022,000D)</t>
+    <t>Pupil dilated - whether pupil was dilated. DICOM (0022,000D)</t>
   </si>
   <si>
     <t>Observation.component:pupilDilated.value[x]</t>
@@ -2231,7 +2231,7 @@
     <t>Observation.component:mydriaticAgent.code</t>
   </si>
   <si>
-    <t>DICOM (0022,000E)</t>
+    <t>Mydriatic agent - dilating agent used. DICOM (0022,000E)</t>
   </si>
   <si>
     <t>Observation.component:mydriaticAgent.value[x]</t>
@@ -2264,7 +2264,7 @@
     <t>Observation.component:dilationDegree.code</t>
   </si>
   <si>
-    <t>DICOM (0022,000F)</t>
+    <t>Degree of dilation - pupil dilation in mm. DICOM (0022,000F)</t>
   </si>
   <si>
     <t>Observation.component:dilationDegree.value[x]</t>
@@ -2298,6 +2298,33 @@
   </si>
   <si>
     <t>Signal strength / Quality - scan quality index</t>
+  </si>
+  <si>
+    <t>Observation.component:signalStrength.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component:signalStrength.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:signalStrength.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component:signalStrength.code.text</t>
+  </si>
+  <si>
+    <t>Observation.component.code.text</t>
+  </si>
+  <si>
+    <t>Signal strength</t>
   </si>
   <si>
     <t>Observation.component:signalStrength.value[x]</t>
@@ -2634,7 +2661,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP258"/>
+  <dimension ref="A1:AP262"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.18359375" customWidth="true" bestFit="true"/>
@@ -4856,7 +4883,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>233</v>
       </c>
@@ -4875,7 +4902,7 @@
         <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
@@ -4978,7 +5005,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>244</v>
       </c>
@@ -4997,7 +5024,7 @@
         <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>83</v>
@@ -7266,7 +7293,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>394</v>
       </c>
@@ -7285,7 +7312,7 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>83</v>
@@ -33501,7 +33528,7 @@
         <v>736</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>485</v>
+        <v>737</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -33521,23 +33548,19 @@
         <v>83</v>
       </c>
       <c r="J255" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>505</v>
+        <v>324</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>486</v>
+        <v>325</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N255" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O255" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N255" s="2"/>
+      <c r="O255" s="2"/>
       <c r="P255" t="s" s="2">
         <v>83</v>
       </c>
@@ -33585,7 +33608,7 @@
         <v>83</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>485</v>
+        <v>327</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>81</v>
@@ -33597,44 +33620,44 @@
         <v>83</v>
       </c>
       <c r="AJ255" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK255" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL255" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AM255" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AN255" t="s" s="2">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="AO255" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP255" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>489</v>
+        <v>739</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E256" s="2"/>
       <c r="F256" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>83</v>
@@ -33646,20 +33669,18 @@
         <v>83</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>490</v>
+        <v>141</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>491</v>
+        <v>330</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O256" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
         <v>83</v>
       </c>
@@ -33683,43 +33704,43 @@
         <v>83</v>
       </c>
       <c r="X256" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y256" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z256" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB256" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="AC256" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="AD256" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE256" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>489</v>
+        <v>334</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH256" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>83</v>
@@ -33728,10 +33749,10 @@
         <v>83</v>
       </c>
       <c r="AM256" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN256" t="s" s="2">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="AO256" t="s" s="2">
         <v>83</v>
@@ -33742,14 +33763,14 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>493</v>
+        <v>741</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
@@ -33765,22 +33786,22 @@
         <v>83</v>
       </c>
       <c r="J257" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>192</v>
+        <v>360</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>295</v>
+        <v>361</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>296</v>
+        <v>362</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>297</v>
+        <v>363</v>
       </c>
       <c r="O257" t="s" s="2">
-        <v>298</v>
+        <v>364</v>
       </c>
       <c r="P257" t="s" s="2">
         <v>83</v>
@@ -33805,13 +33826,13 @@
         <v>83</v>
       </c>
       <c r="X257" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y257" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="Z257" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AA257" t="s" s="2">
         <v>83</v>
@@ -33829,7 +33850,7 @@
         <v>83</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>493</v>
+        <v>365</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>81</v>
@@ -33847,27 +33868,27 @@
         <v>83</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM257" t="s" s="2">
-        <v>302</v>
+        <v>366</v>
       </c>
       <c r="AN257" t="s" s="2">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="AO257" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP257" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>494</v>
+        <v>743</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33878,7 +33899,7 @@
         <v>81</v>
       </c>
       <c r="G258" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H258" t="s" s="2">
         <v>83</v>
@@ -33887,22 +33908,22 @@
         <v>83</v>
       </c>
       <c r="J258" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>495</v>
+        <v>369</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>496</v>
+        <v>370</v>
       </c>
       <c r="N258" t="s" s="2">
-        <v>407</v>
+        <v>371</v>
       </c>
       <c r="O258" t="s" s="2">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>83</v>
@@ -33912,7 +33933,7 @@
         <v>83</v>
       </c>
       <c r="S258" t="s" s="2">
-        <v>83</v>
+        <v>744</v>
       </c>
       <c r="T258" t="s" s="2">
         <v>83</v>
@@ -33951,13 +33972,13 @@
         <v>83</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>494</v>
+        <v>373</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH258" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI258" t="s" s="2">
         <v>83</v>
@@ -33972,20 +33993,508 @@
         <v>83</v>
       </c>
       <c r="AM258" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AN258" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AO258" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP258" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="259" hidden="true">
+      <c r="A259" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C259" s="2"/>
+      <c r="D259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E259" s="2"/>
+      <c r="F259" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G259" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J259" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K259" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L259" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M259" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N259" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O259" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="P259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q259" s="2"/>
+      <c r="R259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF259" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG259" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH259" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ259" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL259" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM259" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AN259" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AO259" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP259" t="s" s="2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="260" hidden="true">
+      <c r="A260" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C260" s="2"/>
+      <c r="D260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E260" s="2"/>
+      <c r="F260" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G260" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K260" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L260" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M260" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N260" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O260" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="P260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q260" s="2"/>
+      <c r="R260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X260" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y260" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z260" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AA260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF260" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG260" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH260" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI260" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AJ260" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM260" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN260" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AO260" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP260" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="261" hidden="true">
+      <c r="A261" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C261" s="2"/>
+      <c r="D261" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="E261" s="2"/>
+      <c r="F261" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G261" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K261" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L261" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M261" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N261" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O261" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q261" s="2"/>
+      <c r="R261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X261" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y261" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="Z261" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AA261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF261" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG261" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH261" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ261" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL261" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM261" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN261" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AO261" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP261" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="262" hidden="true">
+      <c r="A262" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C262" s="2"/>
+      <c r="D262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E262" s="2"/>
+      <c r="F262" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G262" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K262" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L262" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M262" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N262" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O262" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="P262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q262" s="2"/>
+      <c r="R262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF262" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG262" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH262" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ262" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM262" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AN258" t="s" s="2">
+      <c r="AN262" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AO258" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP258" t="s" s="2">
+      <c r="AO262" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP262" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP258">
+  <autoFilter ref="A1:AP262">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -33995,7 +34504,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI257">
+  <conditionalFormatting sqref="A2:AI261">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
